--- a/public/document_tracking.xlsx
+++ b/public/document_tracking.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C60AC0-C3D5-4F09-BC24-79C9D78203E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0484FC2D-2CA4-4FE5-A55F-3230CDD91550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="3990" windowWidth="15660" windowHeight="9848" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dropdown" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>LINK</t>
   </si>
@@ -91,13 +91,16 @@
   </si>
   <si>
     <t>Recieved Documents via QR</t>
+  </si>
+  <si>
+    <t>AMIA Status of Funds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,13 +136,32 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -166,10 +188,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -189,27 +212,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -274,19 +288,35 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="2025-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="2026-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -301,7 +331,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B20">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Dropdown"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="LINK"/>
@@ -508,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.625" customWidth="1"/>
@@ -604,10 +634,10 @@
       </c>
     </row>
     <row r="12" spans="1:2" ht="26" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="8" t="s">
         <v>1</v>
       </c>
     </row>
@@ -664,6 +694,14 @@
         <v>20</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" customHeight="1">
+      <c r="A20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>1</v>
       </c>
     </row>
@@ -679,19 +717,20 @@
     <hyperlink ref="B9" r:id="rId8" location="gid=1840005247" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="B10" r:id="rId9" location="gid=1505714350" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
     <hyperlink ref="B11" r:id="rId10" location="gid=1490275197" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B12" r:id="rId11" location="gid=451356015" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B13" r:id="rId12" location="gid=328484245" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B14" r:id="rId13" location="gid=387609537" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="B15" r:id="rId14" location="gid=2098609058" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B16" r:id="rId15" location="gid=1841021416" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B17" r:id="rId16" location="gid=1817634266" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B19" r:id="rId18" location="gid=115756846" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="B13" r:id="rId11" location="gid=328484245" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B14" r:id="rId12" location="gid=387609537" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="B15" r:id="rId13" location="gid=2098609058" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B16" r:id="rId14" location="gid=1841021416" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B17" r:id="rId15" location="gid=1817634266" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B18" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B19" r:id="rId17" location="gid=115756846" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="B20" r:id="rId18" location="gid=800892725" display="https://docs.google.com/spreadsheets/d/1wSNta-v-unsP5EvxZe5q1oA2YG0lF-xa/edit?gid=800892725 - gid=800892725" xr:uid="{870420F9-876C-4D4C-AF62-95C2DE8A2093}"/>
+    <hyperlink ref="B12" r:id="rId19" display="https://docs.google.com/spreadsheets/d/1sGCV91KQfms2yuTF2iwuEz5o0SACouTTJKfRyZ1VrKA/edit?usp=sharing" xr:uid="{A8EE41C2-9C8E-40AF-80D0-E636A0769FBE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId20"/>
   <tableParts count="1">
-    <tablePart r:id="rId19"/>
+    <tablePart r:id="rId21"/>
   </tableParts>
 </worksheet>
 </file>
--- a/public/document_tracking.xlsx
+++ b/public/document_tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0484FC2D-2CA4-4FE5-A55F-3230CDD91550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F184D57D-2F78-4F53-A405-AA103C8DA916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,12 +123,6 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -190,7 +184,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -209,14 +203,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -634,10 +628,10 @@
       </c>
     </row>
     <row r="12" spans="1:2" ht="26" customHeight="1">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -685,7 +679,7 @@
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>1</v>
       </c>
     </row>
@@ -698,10 +692,10 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" customHeight="1">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -722,10 +716,10 @@
     <hyperlink ref="B15" r:id="rId13" location="gid=2098609058" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
     <hyperlink ref="B16" r:id="rId14" location="gid=1841021416" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
     <hyperlink ref="B17" r:id="rId15" location="gid=1817634266" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B18" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B19" r:id="rId17" location="gid=115756846" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="B20" r:id="rId18" location="gid=800892725" display="https://docs.google.com/spreadsheets/d/1wSNta-v-unsP5EvxZe5q1oA2YG0lF-xa/edit?gid=800892725 - gid=800892725" xr:uid="{870420F9-876C-4D4C-AF62-95C2DE8A2093}"/>
-    <hyperlink ref="B12" r:id="rId19" display="https://docs.google.com/spreadsheets/d/1sGCV91KQfms2yuTF2iwuEz5o0SACouTTJKfRyZ1VrKA/edit?usp=sharing" xr:uid="{A8EE41C2-9C8E-40AF-80D0-E636A0769FBE}"/>
+    <hyperlink ref="B19" r:id="rId16" location="gid=115756846" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="B20" r:id="rId17" location="gid=800892725" display="https://docs.google.com/spreadsheets/d/1wSNta-v-unsP5EvxZe5q1oA2YG0lF-xa/edit?gid=800892725 - gid=800892725" xr:uid="{870420F9-876C-4D4C-AF62-95C2DE8A2093}"/>
+    <hyperlink ref="B12" r:id="rId18" display="https://docs.google.com/spreadsheets/d/1sGCV91KQfms2yuTF2iwuEz5o0SACouTTJKfRyZ1VrKA/edit?usp=sharing" xr:uid="{A8EE41C2-9C8E-40AF-80D0-E636A0769FBE}"/>
+    <hyperlink ref="B18" r:id="rId19" location="gid=8330880" display="https://docs.google.com/spreadsheets/d/16xng3LBmgNAlBtB115t8ZWzPoPOxXUUQ/edit?gid=8330880 - gid=8330880" xr:uid="{A54D9351-9162-4124-81A0-026C86ABDB35}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId20"/>

--- a/public/document_tracking.xlsx
+++ b/public/document_tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaica\OneDrive\Desktop\PS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F184D57D-2F78-4F53-A405-AA103C8DA916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB507FD8-0D9A-4BE9-AC0E-B77FF886E29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21075" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
     <t>LINK</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>AMIA Status of Funds</t>
+  </si>
+  <si>
+    <t>Scanned Documents</t>
   </si>
 </sst>
 </file>
@@ -144,7 +147,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +157,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -186,7 +195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -211,6 +220,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -325,7 +340,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B21">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Dropdown"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="LINK"/>
@@ -532,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.625" customWidth="1"/>
@@ -696,6 +711,14 @@
         <v>21</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -720,11 +743,12 @@
     <hyperlink ref="B20" r:id="rId17" location="gid=800892725" display="https://docs.google.com/spreadsheets/d/1wSNta-v-unsP5EvxZe5q1oA2YG0lF-xa/edit?gid=800892725 - gid=800892725" xr:uid="{870420F9-876C-4D4C-AF62-95C2DE8A2093}"/>
     <hyperlink ref="B12" r:id="rId18" display="https://docs.google.com/spreadsheets/d/1sGCV91KQfms2yuTF2iwuEz5o0SACouTTJKfRyZ1VrKA/edit?usp=sharing" xr:uid="{A8EE41C2-9C8E-40AF-80D0-E636A0769FBE}"/>
     <hyperlink ref="B18" r:id="rId19" location="gid=8330880" display="https://docs.google.com/spreadsheets/d/16xng3LBmgNAlBtB115t8ZWzPoPOxXUUQ/edit?gid=8330880 - gid=8330880" xr:uid="{A54D9351-9162-4124-81A0-026C86ABDB35}"/>
+    <hyperlink ref="B21" r:id="rId20" display="https://darfoxiii-my.sharepoint.com/my?id=%2Fpersonal%2Famia%5Fcaraga%5Fda%5Fgov%5Fph%2FDocuments%2F2026%20WORKING%20FILES%2FSCANNED%20DOCUMENTS%2DAPPROVED&amp;viewid=a922d1ac%2Da10a%2D4277%2D80dc%2Dd5261e478759" xr:uid="{21F5629F-FB6D-41E4-9AF5-54392446BB1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId20"/>
+  <pageSetup orientation="landscape" r:id="rId21"/>
   <tableParts count="1">
-    <tablePart r:id="rId21"/>
+    <tablePart r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>